--- a/output/pdf_financials_xlsx/MON.xlsx
+++ b/output/pdf_financials_xlsx/MON.xlsx
@@ -5774,49 +5774,49 @@
         <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
-        <v>0</v>
+        <v>-0.07953499999999999</v>
       </c>
       <c r="E91" s="3" t="n">
-        <v>0</v>
+        <v>-0.236713</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0</v>
+        <v>0.269413</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0</v>
+        <v>0.943738</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0</v>
+        <v>1.10531</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0</v>
+        <v>1.072992</v>
       </c>
       <c r="J91" s="3" t="n">
-        <v>0</v>
+        <v>0.995765</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0</v>
+        <v>1.045113</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0</v>
+        <v>1.050898</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0</v>
+        <v>1.04756</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>0</v>
+        <v>1.04756</v>
       </c>
       <c r="O91" s="3" t="n">
-        <v>0</v>
+        <v>1.04756</v>
       </c>
       <c r="P91" s="3" t="n">
-        <v>0</v>
+        <v>1.04756</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>0</v>
+        <v>1.04756</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>0</v>
+        <v>1.04756</v>
       </c>
     </row>
     <row r="92">
@@ -5829,52 +5829,52 @@
         <v>0.305172</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.869304</v>
+        <v>0.305172</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>6.275418</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>6.275418</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>6.871179</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>6.871179</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>6.871179</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>6.871179</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>6.871179</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>7.292626</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>7.292626</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>8.110635</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>8.080043</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>8.836549</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>8.836549</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>10.285783</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>10.325689</v>
       </c>
     </row>
     <row r="93">
@@ -9710,7 +9710,11 @@
           <t>Share based payment reserve 9</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -9809,7 +9813,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -10506,7 +10514,11 @@
           <t>Share based payment reserve 9</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -10605,7 +10617,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -11607,7 +11623,11 @@
           <t>Share based payment reserve 8</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -11706,7 +11726,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -12421,7 +12445,11 @@
           <t>Share based payment reserve 8</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -12825,7 +12853,11 @@
           <t>Share based payment reserve 8</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -13603,7 +13635,11 @@
           <t>Share-based payment reserve 12</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -13700,7 +13736,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -14496,7 +14536,11 @@
           <t>Share-based payment reserve 12</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -14591,7 +14635,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -15353,7 +15401,11 @@
           <t>Warrant reserve 12</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -15450,7 +15502,11 @@
           <t>Share-based payment reserve 13</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -16343,7 +16399,11 @@
           <t>Warrant reserve 13</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -16440,7 +16500,11 @@
           <t>Share-based payment reserve 14</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>
@@ -18894,7 +18958,11 @@
           <t>Warrant reserve 12 4,559,975</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -18995,7 +19063,11 @@
           <t>Share-based payment reserve 13 1,715,443</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -19094,7 +19166,11 @@
           <t>Foreign currency translation reserve 57,881</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MON.xlsx
+++ b/output/pdf_financials_xlsx/MON.xlsx
@@ -1029,16 +1029,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000357</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.002364</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.041611</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.011126</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1059,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>2e-06</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
@@ -1975,16 +1975,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.39041</v>
+        <v>-0.390767</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.00142</v>
+        <v>-1.003784</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.204192</v>
+        <v>-3.245803</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.368271</v>
+        <v>-3.379397</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-0.910158</v>
@@ -2005,7 +2005,7 @@
         <v>-3.669089</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.6575569999999999</v>
+        <v>-0.657559</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-0.733166</v>
@@ -2091,16 +2091,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.39041</v>
+        <v>-0.390767</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.989184</v>
+        <v>-0.991548</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.186516</v>
+        <v>-3.228127</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.326984</v>
+        <v>-3.33811</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.878474</v>
@@ -2121,7 +2121,7 @@
         <v>-3.665325</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.6564990000000001</v>
+        <v>-0.656501</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-0.732387</v>
@@ -2413,40 +2413,40 @@
         <v>0.024406</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.02508</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.008878</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.004589</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.22258</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.032758</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.010979</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.704095</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.241178</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.004718</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.009641</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.417527</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.016742</v>
       </c>
     </row>
     <row r="35">
@@ -2529,40 +2529,40 @@
         <v>0.024406</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.02508</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.008878</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.004589</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.22258</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.032758</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.010979</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.704095</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.241178</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.004718</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.009641</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.417527</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.016742</v>
       </c>
     </row>
     <row r="37">
@@ -3225,40 +3225,40 @@
         <v>1.414327</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.027098</v>
+        <v>0.002018</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.016578</v>
+        <v>0.0077</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.010829</v>
+        <v>0.00624</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.238512</v>
+        <v>0.015932</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.047995</v>
+        <v>0.015237</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.029702</v>
+        <v>0.018723</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.747353</v>
+        <v>0.043258</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.290725</v>
+        <v>0.049547</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.033804</v>
+        <v>0.029086</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.03953</v>
+        <v>0.029889</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.965874</v>
+        <v>0.548347</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>2.329627</v>
+        <v>2.312885</v>
       </c>
     </row>
     <row r="49">
@@ -8537,7 +8537,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -13061,7 +13061,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -40620,7 +40620,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -41826,7 +41826,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -43020,7 +43020,7 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
@@ -45313,7 +45313,7 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
@@ -46285,7 +46285,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E382" s="5" t="n">

--- a/output/pdf_financials_xlsx/MON.xlsx
+++ b/output/pdf_financials_xlsx/MON.xlsx
@@ -858,7 +858,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>0.022649</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0</v>
@@ -916,7 +916,7 @@
         <v>0.180651</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.400493</v>
+        <v>0.423142</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0</v>
@@ -58681,7 +58681,11 @@
           <t>Rent and occupancy costs (Note 10)</t>
         </is>
       </c>
-      <c r="D506" t="inlineStr"/>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E506" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MON.xlsx
+++ b/output/pdf_financials_xlsx/MON.xlsx
@@ -739,10 +739,10 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.180651</v>
+        <v>0.19586</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.400493</v>
+        <v>0.418735</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0</v>
@@ -772,10 +772,10 @@
         <v>0.283428</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.275907</v>
+        <v>0.0395</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0</v>
+        <v>0.0395</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>0</v>
@@ -784,10 +784,10 @@
         <v>0</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.19877</v>
+        <v>0.231937</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>1.577158</v>
+        <v>1.616658</v>
       </c>
     </row>
     <row r="8">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.180651</v>
+        <v>0.19586</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.423142</v>
+        <v>0.441384</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         <v>-0.39041</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-1.00142</v>
+        <v>-0.938557</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-3.204192</v>
@@ -1322,7 +1322,7 @@
         <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.062863</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0</v>
@@ -1978,7 +1978,7 @@
         <v>-0.390767</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.003784</v>
+        <v>-0.940921</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-3.245803</v>
@@ -2094,7 +2094,7 @@
         <v>-0.390767</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.991548</v>
+        <v>-0.928685</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-3.228127</v>
@@ -2244,7 +2244,7 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>-6.697835080874151</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -4356,49 +4356,49 @@
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.072371</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.081395</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.251025</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.254179</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.177414</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.08092000000000001</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.10241</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.104328</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.089721</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.026281</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.032693</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.061</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.117</v>
       </c>
     </row>
     <row r="68">
@@ -4414,49 +4414,49 @@
         <v>0.201576</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>1.071596</v>
+        <v>1.143967</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>1.576623</v>
+        <v>1.658018</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.840769</v>
+        <v>1.091794</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>1.105675</v>
+        <v>1.359854</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>1.177576</v>
+        <v>1.35499</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.311138</v>
+        <v>0.392058</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.197371</v>
+        <v>0.277071</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0.282349</v>
+        <v>0.384759</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.549288</v>
+        <v>0.653616</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>0.415869</v>
+        <v>0.50559</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>0.438969</v>
+        <v>0.46525</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>0.70253</v>
+        <v>0.735223</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>1.356969</v>
+        <v>1.417969</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>0.528734</v>
+        <v>0.561734</v>
       </c>
       <c r="R68" s="3" t="n">
-        <v>0.292685</v>
+        <v>0.409685</v>
       </c>
     </row>
     <row r="69">
@@ -6882,7 +6882,7 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.043298</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -6897,16 +6897,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002185</v>
       </c>
       <c r="I111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.0009</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001556</v>
       </c>
       <c r="L111" s="3" t="n">
         <v>0</v>
@@ -8286,7 +8286,7 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.043298</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -8301,16 +8301,16 @@
         <v>0</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002185</v>
       </c>
       <c r="I134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.0009</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001556</v>
       </c>
       <c r="L134" s="3" t="n">
         <v>0</v>
@@ -8344,7 +8344,7 @@
         <v>-0.183617</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.600542</v>
+        <v>-0.64384</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-1.342824</v>
@@ -8359,16 +8359,16 @@
         <v>-0.013303</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-0.108413</v>
+        <v>-0.110598</v>
       </c>
       <c r="I135" s="3" t="n">
         <v>-0.03239</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-0.357672</v>
+        <v>-0.358572</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-0.52132</v>
+        <v>-0.522876</v>
       </c>
       <c r="L135" s="3" t="n">
         <v>-0.020648</v>
@@ -28312,7 +28312,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -32941,7 +32945,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -35076,7 +35084,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>-</t>
@@ -36290,7 +36302,11 @@
           <t>Directors' fees 11</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
@@ -41725,7 +41741,11 @@
           <t>Directors' fee 10</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr"/>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E336" t="inlineStr">
         <is>
           <t>-</t>
@@ -56451,7 +56471,11 @@
           <t>Deferred income tax recovery 14</t>
         </is>
       </c>
-      <c r="D484" t="inlineStr"/>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E484" t="inlineStr">
         <is>
           <t>-</t>
@@ -57861,7 +57885,11 @@
           <t>Directors’ fees (Note 10)</t>
         </is>
       </c>
-      <c r="D498" t="inlineStr"/>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E498" s="5" t="n">
         <v>0.015209</v>
       </c>
